--- a/modelos_importacao/Modelo_Importacao_Projetos.xlsx
+++ b/modelos_importacao/Modelo_Importacao_Projetos.xlsx
@@ -400,18 +400,18 @@
   <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="22.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="45.83203125" customWidth="1"/>
+    <col min="11" max="11" width="28.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
